--- a/kicad/bom.xlsx
+++ b/kicad/bom.xlsx
@@ -5,18 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Projects\e-reader v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markh\Programming\github\esp-reader\kicad\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{FCA8B0D5-741E-42E0-9CF4-E3E2449DE0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="15600" windowHeight="18720" xr2:uid="{65A41742-40FE-41A2-B90A-5019F622817B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{65A41742-40FE-41A2-B90A-5019F622817B}"/>
   </bookViews>
   <sheets>
     <sheet name="e-reader" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -982,10 +981,6 @@
     </a>
   </bag>
 </FeaturePropertyBags>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1306,19 +1301,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB01CF19-F1F7-4B08-9BFE-6910450CB408}">
   <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="2.5703125" customWidth="1"/>
+    <col min="1" max="1" width="33.7265625" customWidth="1"/>
+    <col min="3" max="3" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="2.54296875" customWidth="1"/>
     <col min="8" max="8" width="3" customWidth="1"/>
-    <col min="9" max="9" width="68.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.140625" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" customWidth="1"/>
-    <col min="12" max="12" width="127.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="68.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.1796875" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" customWidth="1"/>
+    <col min="12" max="12" width="127.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1356,7 +1351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>129</v>
       </c>
@@ -1379,7 +1374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>128</v>
       </c>
@@ -1402,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1425,7 +1420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1448,7 +1443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1471,7 +1466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1497,7 +1492,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1520,7 +1515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1546,7 +1541,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>123</v>
       </c>
@@ -1572,7 +1567,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1598,7 +1593,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -1624,7 +1619,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1647,7 +1642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -1673,7 +1668,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1696,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1722,7 +1717,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>127</v>
       </c>
@@ -1748,7 +1743,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -1771,7 +1766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -1794,7 +1789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -1817,7 +1812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1840,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -1863,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -1886,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -1909,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -1932,7 +1927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -1955,7 +1950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>71</v>
       </c>
@@ -1981,7 +1976,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>75</v>
       </c>
@@ -2007,7 +2002,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>79</v>
       </c>
@@ -2033,7 +2028,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>83</v>
       </c>
@@ -2056,7 +2051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -2079,7 +2074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>89</v>
       </c>
@@ -2102,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -2125,7 +2120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>93</v>
       </c>
@@ -2148,7 +2143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>95</v>
       </c>
@@ -2171,7 +2166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>97</v>
       </c>
@@ -2194,7 +2189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>99</v>
       </c>
@@ -2217,7 +2212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>101</v>
       </c>
@@ -2240,7 +2235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>103</v>
       </c>
@@ -2263,7 +2258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>105</v>
       </c>
@@ -2289,7 +2284,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>109</v>
       </c>
@@ -2315,7 +2310,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>113</v>
       </c>
